--- a/code_notebooks/implementasi/rekap_kombinasi_parameter_base_dan_meta.xlsx
+++ b/code_notebooks/implementasi/rekap_kombinasi_parameter_base_dan_meta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,11 +467,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8247075107452465</v>
+        <v>0.8554895572191018</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -488,11 +488,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8241684271872952</v>
+        <v>0.8479730260916659</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -509,11 +509,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.813378014132731</v>
+        <v>0.8162131707444903</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -530,11 +530,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.811218765935747</v>
+        <v>0.81496056114115</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -551,11 +551,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8096029722444816</v>
+        <v>0.8149561936041788</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -572,11 +572,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8090624317039412</v>
+        <v>0.8141263615796508</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -593,11 +593,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8085233481459897</v>
+        <v>0.812038678907417</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -614,11 +614,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.798272018649377</v>
+        <v>0.8070299875088442</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7971923945508851</v>
+        <v>0.8040993702011686</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -656,11 +656,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7966664238362352</v>
+        <v>0.8032625501174868</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -677,11 +677,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7842529321774604</v>
+        <v>0.8028423930608574</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7783259270051722</v>
+        <v>0.7990906788025961</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -719,11 +719,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7777737306039192</v>
+        <v>0.7978424367362269</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -740,11 +740,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7766999344357834</v>
+        <v>0.7974222796795974</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -761,11 +761,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7766926495228381</v>
+        <v>0.7974161651278378</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7734654330880746</v>
+        <v>0.7957512600344161</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -803,14 +803,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7734654330880746</v>
+        <v>0.7957477660048392</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -824,11 +824,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.7702280177751877</v>
+        <v>0.7944934093867104</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.7686093101187441</v>
+        <v>0.7911539906185305</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.7626691921031543</v>
+        <v>0.781550650326255</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -887,11 +887,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7583623515698987</v>
+        <v>0.7807147037499673</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7529671450426167</v>
+        <v>0.7794647146688097</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -929,11 +929,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.7524251475194872</v>
+        <v>0.77779194800884</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.7513484373861732</v>
+        <v>0.7748665717455299</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -971,11 +971,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.7508122677933999</v>
+        <v>0.7652562433941003</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -992,11 +992,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.7486515626138268</v>
+        <v>0.764847441933596</v>
       </c>
       <c r="E27" t="n">
         <v>26</v>
@@ -1013,11 +1013,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7427201864937714</v>
+        <v>0.764422043832601</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -1034,14 +1034,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.7378611495592627</v>
+        <v>0.764422043832601</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1055,11 +1055,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.7373249799664894</v>
+        <v>0.7644176762956298</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1076,14 +1076,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.7373220660013112</v>
+        <v>0.7644176762956298</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7367858964085379</v>
+        <v>0.7631694342292608</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1118,14 +1118,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.7362409849202303</v>
+        <v>0.7631694342292608</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1139,11 +1139,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.736235156989874</v>
+        <v>0.7631676872144723</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.736235156989874</v>
+        <v>0.7631676872144723</v>
       </c>
       <c r="E35" t="n">
         <v>33</v>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.7357135572229913</v>
+        <v>0.7623308671307903</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1202,11 +1202,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.7351584468565602</v>
+        <v>0.7619159511185262</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1223,14 +1223,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.7340904786187805</v>
+        <v>0.7619159511185262</v>
       </c>
       <c r="E38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
@@ -1244,11 +1244,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.7340890216361914</v>
+        <v>0.7619142041037377</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1265,11 +1265,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.7340890216361914</v>
+        <v>0.7619142041037377</v>
       </c>
       <c r="E40" t="n">
         <v>38</v>
@@ -1286,14 +1286,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.7340890216361914</v>
+        <v>0.7610826250644211</v>
       </c>
       <c r="E41" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1307,11 +1307,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.7340802797406571</v>
+        <v>0.7602449314733449</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1328,11 +1328,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.7340802797406571</v>
+        <v>0.7602449314733449</v>
       </c>
       <c r="E43" t="n">
         <v>41</v>
@@ -1349,11 +1349,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.7324703139797479</v>
+        <v>0.7589923218700046</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.7324586581190354</v>
+        <v>0.7564897231855067</v>
       </c>
       <c r="E45" t="n">
         <v>44</v>
@@ -1391,14 +1391,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.7324586581190354</v>
+        <v>0.7543941789467249</v>
       </c>
       <c r="E46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -1412,11 +1412,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.7308501493407153</v>
+        <v>0.753976642412278</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1433,11 +1433,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.7308501493407153</v>
+        <v>0.753976642412278</v>
       </c>
       <c r="E48" t="n">
         <v>46</v>
@@ -1454,11 +1454,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.7308443214103592</v>
+        <v>0.7535652204295908</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.7303066948349967</v>
+        <v>0.7527310208680916</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.7292299847016828</v>
+        <v>0.7527310208680916</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.7292299847016828</v>
+        <v>0.7527310208680916</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.7292299847016828</v>
+        <v>0.7527292738533031</v>
       </c>
       <c r="E53" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -1559,14 +1559,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.7270736504698769</v>
+        <v>0.7527292738533031</v>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55">
@@ -1580,11 +1580,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.7254520288482553</v>
+        <v>0.7523082432892794</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1601,14 +1601,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.7254520288482553</v>
+        <v>0.7510573807007276</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
@@ -1622,11 +1622,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.72491877322066</v>
+        <v>0.7502275486761996</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.72491877322066</v>
+        <v>0.7489696980284938</v>
       </c>
       <c r="E58" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -1664,11 +1664,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.7227566110584979</v>
+        <v>0.7460425747503953</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1685,11 +1685,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.7211495592627668</v>
+        <v>0.7456154296346119</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1706,11 +1706,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.7195148247978436</v>
+        <v>0.7401865811794097</v>
       </c>
       <c r="E61" t="n">
         <v>60</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.7168237779558534</v>
+        <v>0.7385225495933823</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1748,11 +1748,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.7103431193997232</v>
+        <v>0.7368558974851721</v>
       </c>
       <c r="E63" t="n">
         <v>62</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.7071042471042471</v>
+        <v>0.7226605288213765</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.550187222262694</v>
+        <v>0.5500965225670635</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.550187222262694</v>
+        <v>0.5500965225670635</v>
       </c>
       <c r="E66" t="n">
         <v>64</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.550187222262694</v>
+        <v>0.5500965225670635</v>
       </c>
       <c r="E67" t="n">
         <v>64</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.5172492168718584</v>
+        <v>0.4924764808134102</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.5172492168718584</v>
+        <v>0.4924764808134102</v>
       </c>
       <c r="E69" t="n">
         <v>67</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.5172492168718584</v>
+        <v>0.4924764808134102</v>
       </c>
       <c r="E70" t="n">
         <v>67</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.500001456982589</v>
+        <v>0.4766100925044331</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.500001456982589</v>
+        <v>0.4766100925044331</v>
       </c>
       <c r="E72" t="n">
         <v>70</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.500001456982589</v>
+        <v>0.4766100925044331</v>
       </c>
       <c r="E73" t="n">
         <v>70</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.943914912216799</v>
+        <v>0.9644945449463231</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2000,11 +2000,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.94391345523421</v>
+        <v>0.9632401883281944</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -2021,14 +2021,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.94391345523421</v>
+        <v>0.9632375678060114</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.9439105412690317</v>
+        <v>0.9628217782863533</v>
       </c>
       <c r="E77" t="n">
         <v>4</v>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.9439105412690317</v>
+        <v>0.9628200312715649</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -2084,11 +2084,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.9428294601879508</v>
+        <v>0.9619867052174598</v>
       </c>
       <c r="E79" t="n">
         <v>6</v>
@@ -2105,14 +2105,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.9428294601879508</v>
+        <v>0.9619858317100654</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2126,14 +2126,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.9412151234792743</v>
+        <v>0.9619858317100654</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2147,14 +2147,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.9412151234792743</v>
+        <v>0.9611516321485662</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.94068041086909</v>
+        <v>0.9611507586411718</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.9401398703285496</v>
+        <v>0.9611498851337779</v>
       </c>
       <c r="E84" t="n">
         <v>11</v>
@@ -2210,14 +2210,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.9401398703285496</v>
+        <v>0.9607349691215138</v>
       </c>
       <c r="E85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -2231,14 +2231,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.9401398703285496</v>
+        <v>0.9607340956141194</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.9390558752822905</v>
+        <v>0.9603148120648843</v>
       </c>
       <c r="E87" t="n">
         <v>14</v>
@@ -2273,14 +2273,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.9390558752822905</v>
+        <v>0.8508826792218797</v>
       </c>
       <c r="E88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89">
@@ -2294,11 +2294,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.9379791651489764</v>
+        <v>0.8492055450249387</v>
       </c>
       <c r="E89" t="n">
         <v>16</v>
@@ -2315,11 +2315,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.9363619144751221</v>
+        <v>0.8329155056297551</v>
       </c>
       <c r="E90" t="n">
         <v>17</v>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.93528229037663</v>
+        <v>0.8304094129156804</v>
       </c>
       <c r="E91" t="n">
         <v>18</v>
@@ -2357,14 +2357,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.93528229037663</v>
+        <v>0.824146364898979</v>
       </c>
       <c r="E92" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
@@ -2378,11 +2378,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.9352808333940409</v>
+        <v>0.8212218621430629</v>
       </c>
       <c r="E93" t="n">
         <v>20</v>
@@ -2399,11 +2399,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.9347446638012675</v>
+        <v>0.8091080615997415</v>
       </c>
       <c r="E94" t="n">
         <v>21</v>
@@ -2420,11 +2420,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.9347432068186785</v>
+        <v>0.8066054629152436</v>
       </c>
       <c r="E95" t="n">
         <v>22</v>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.9347432068186785</v>
+        <v>0.8049309492404854</v>
       </c>
       <c r="E96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
@@ -2462,11 +2462,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.9315057915057915</v>
+        <v>0.79991963731973</v>
       </c>
       <c r="E97" t="n">
         <v>24</v>
@@ -2483,11 +2483,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.8500604647774459</v>
+        <v>0.7978345751696787</v>
       </c>
       <c r="E98" t="n">
         <v>25</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.8500604647774459</v>
+        <v>0.7957468924974449</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.8398120492460116</v>
+        <v>0.7915645390938233</v>
       </c>
       <c r="E100" t="n">
         <v>27</v>
@@ -2546,11 +2546,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.8300939753769943</v>
+        <v>0.7857286361929054</v>
       </c>
       <c r="E101" t="n">
         <v>28</v>
@@ -2562,19 +2562,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.8284854665986743</v>
+        <v>0.7552353665673779</v>
       </c>
       <c r="E102" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2583,19 +2583,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.8284854665986743</v>
+        <v>0.7552275050008299</v>
       </c>
       <c r="E103" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2604,19 +2604,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.8203861003861004</v>
+        <v>0.7518942007844096</v>
       </c>
       <c r="E104" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2625,19 +2625,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.81661251548044</v>
+        <v>0.7518942007844096</v>
       </c>
       <c r="E105" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2646,19 +2646,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.81661251548044</v>
+        <v>0.7518942007844096</v>
       </c>
       <c r="E106" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -2667,19 +2667,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.8117549355285204</v>
+        <v>0.7518942007844096</v>
       </c>
       <c r="E107" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -2688,19 +2688,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.8096015152618927</v>
+        <v>0.7518942007844096</v>
       </c>
       <c r="E108" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -2709,19 +2709,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.8096015152618927</v>
+        <v>0.7518942007844096</v>
       </c>
       <c r="E109" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -2730,19 +2730,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.8020485175202158</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E110" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
@@ -2751,19 +2751,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.8020485175202158</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E111" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
@@ -2772,19 +2772,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.7869439790194507</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E112" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
@@ -2793,19 +2793,19 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.7853252713630072</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E113" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
@@ -2814,19 +2814,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.7853252713630072</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E114" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
@@ -2835,19 +2835,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.7837109346543308</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E115" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
@@ -2856,19 +2856,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.7810111459168063</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E116" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117">
@@ -2877,19 +2877,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.7788518977198222</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E117" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
@@ -2898,19 +2898,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.7788518977198222</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E118" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
@@ -2919,19 +2919,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.7761579369126539</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E119" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
@@ -2940,19 +2940,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.7756203103372915</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E120" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121">
@@ -2961,19 +2961,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.7756203103372915</v>
+        <v>0.7514766642499628</v>
       </c>
       <c r="E121" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
@@ -2987,14 +2987,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.7481183069862316</v>
+        <v>0.7510591277155162</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123">
@@ -3008,14 +3008,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.7427158155460042</v>
+        <v>0.7506407176736751</v>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.7340861076710133</v>
+        <v>0.7506407176736751</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.7308559772710715</v>
+        <v>0.7506407176736751</v>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.730315436730531</v>
+        <v>0.7502231811392284</v>
       </c>
       <c r="E126" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127">
@@ -3092,14 +3092,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.7292328986668609</v>
+        <v>0.7502223076318341</v>
       </c>
       <c r="E127" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128">
@@ -3113,14 +3113,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.7286952720914985</v>
+        <v>0.7498038975899931</v>
       </c>
       <c r="E128" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
@@ -3134,14 +3134,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.7286923581263205</v>
+        <v>0.7498012770678104</v>
       </c>
       <c r="E129" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.7286909011437313</v>
+        <v>0.7493863610555463</v>
       </c>
       <c r="E130" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131">
@@ -3176,14 +3176,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.7276141910104175</v>
+        <v>0.7489705715358881</v>
       </c>
       <c r="E131" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132">
@@ -3197,14 +3197,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.7276112770452393</v>
+        <v>0.7481346249596003</v>
       </c>
       <c r="E132" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133">
@@ -3218,14 +3218,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.7270736504698768</v>
+        <v>0.7481328779448118</v>
       </c>
       <c r="E133" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134">
@@ -3239,14 +3239,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7468802683414715</v>
       </c>
       <c r="E134" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135">
@@ -3260,14 +3260,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7456285322455255</v>
       </c>
       <c r="E135" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
@@ -3281,14 +3281,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7456276587381312</v>
       </c>
       <c r="E136" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7443706815978197</v>
       </c>
       <c r="E137" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138">
@@ -3323,14 +3323,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7418663358985335</v>
       </c>
       <c r="E138" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="139">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7414496728714809</v>
       </c>
       <c r="E139" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7406137262951932</v>
       </c>
       <c r="E140" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="141">
@@ -3386,14 +3386,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7368567709925665</v>
       </c>
       <c r="E141" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7343471842489147</v>
       </c>
       <c r="E142" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143">
@@ -3428,14 +3428,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.7265331099293363</v>
+        <v>0.7330980686751513</v>
       </c>
       <c r="E143" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144">
@@ -3449,14 +3449,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.7259998543017411</v>
+        <v>0.7322664896358348</v>
       </c>
       <c r="E144" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145">
@@ -3470,14 +3470,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.7259983973191521</v>
+        <v>0.7264104960648492</v>
       </c>
       <c r="E145" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146">
@@ -3491,14 +3491,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.7259940263713848</v>
+        <v>0.7176570784671693</v>
       </c>
       <c r="E146" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147">
@@ -3512,14 +3512,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.7259940263713848</v>
+        <v>0.7138695504057442</v>
       </c>
       <c r="E147" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="148">
@@ -3533,14 +3533,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.7259940263713848</v>
+        <v>0.6854499873341429</v>
       </c>
       <c r="E148" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.7254549428134334</v>
+        <v>0.6082293131611359</v>
       </c>
       <c r="E149" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="150">
@@ -3575,14 +3575,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.7254549428134334</v>
+        <v>0.5592858203544694</v>
       </c>
       <c r="E150" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="151">
@@ -3596,14 +3596,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.7254549428134334</v>
+        <v>0.5480140809391951</v>
       </c>
       <c r="E151" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="152">
@@ -3617,14 +3617,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.7254549428134334</v>
+        <v>0.5467562302914895</v>
       </c>
       <c r="E152" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="153">
@@ -3638,14 +3638,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.7254549428134334</v>
+        <v>0.5116831613979611</v>
       </c>
       <c r="E153" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
     </row>
     <row r="154">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.7254534858308442</v>
+        <v>0.5024973576401324</v>
       </c>
       <c r="E154" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="155">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.7249129452903038</v>
+        <v>0.5012447480367921</v>
       </c>
       <c r="E155" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="156">
@@ -3701,14 +3701,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.7249129452903038</v>
+        <v>0.5008272115023453</v>
       </c>
       <c r="E156" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157">
@@ -3722,14 +3722,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.7238376921395788</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E157" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="158">
@@ -3743,14 +3743,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.721682814890362</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E158" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="159">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.7216784439425948</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E159" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.7189932250309609</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E160" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="161">
@@ -3806,14 +3806,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.7184410286297078</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E161" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="162">
@@ -3822,19 +3822,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.7173686894441612</v>
+        <v>0.9348398424192661</v>
       </c>
       <c r="E162" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -3843,19 +3843,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.7168281489036207</v>
+        <v>0.8809627798499315</v>
       </c>
       <c r="E163" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -3864,19 +3864,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.715206527281999</v>
+        <v>0.8425293280107617</v>
       </c>
       <c r="E164" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -3885,19 +3885,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.7108953158009762</v>
+        <v>0.8112027323311292</v>
       </c>
       <c r="E165" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
@@ -3906,19 +3906,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.7038945144605522</v>
+        <v>0.8020081934993579</v>
       </c>
       <c r="E166" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -3927,19 +3927,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.6952604356377942</v>
+        <v>0.7928215162341349</v>
       </c>
       <c r="E167" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
@@ -3948,19 +3948,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.6397056895170102</v>
+        <v>0.7844751530821709</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -3969,19 +3969,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.6375697530414511</v>
+        <v>0.7769577484473407</v>
       </c>
       <c r="E169" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -3990,19 +3990,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.5750273184235448</v>
+        <v>0.7460443217651838</v>
       </c>
       <c r="E170" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171">
@@ -4011,19 +4011,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.5636832519851389</v>
+        <v>0.7460443217651838</v>
       </c>
       <c r="E171" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -4032,19 +4032,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.5156436220587164</v>
+        <v>0.7452092486962902</v>
       </c>
       <c r="E172" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173">
@@ -4053,19 +4053,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.500001456982589</v>
+        <v>0.7452092486962902</v>
       </c>
       <c r="E173" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174">
@@ -4074,19 +4074,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.500001456982589</v>
+        <v>0.7439557655855558</v>
       </c>
       <c r="E174" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
@@ -4095,19 +4095,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.500001456982589</v>
+        <v>0.7439557655855558</v>
       </c>
       <c r="E175" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -4116,19 +4116,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.499998543017411</v>
+        <v>0.7422847459403744</v>
       </c>
       <c r="E176" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177">
@@ -4137,19 +4137,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.499998543017411</v>
+        <v>0.7397751591967225</v>
       </c>
       <c r="E177" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178">
@@ -4158,19 +4158,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.499998543017411</v>
+        <v>0.7397751591967225</v>
       </c>
       <c r="E178" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179">
@@ -4179,19 +4179,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.499998543017411</v>
+        <v>0.7360199509088845</v>
       </c>
       <c r="E179" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180">
@@ -4200,19 +4200,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.499998543017411</v>
+        <v>0.7356041613892261</v>
       </c>
       <c r="E180" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181">
@@ -4221,439 +4221,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.4892168718583813</v>
+        <v>0.7356041613892261</v>
       </c>
       <c r="E181" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>0.9185590442194217</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>0.8657011728709841</v>
-      </c>
-      <c r="E183" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>0.8306374298827131</v>
-      </c>
-      <c r="E184" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>0.7988125591899177</v>
-      </c>
-      <c r="E185" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>0.7923420995119108</v>
-      </c>
-      <c r="E186" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>0.772919064617178</v>
-      </c>
-      <c r="E187" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>0.7610592263422452</v>
-      </c>
-      <c r="E188" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>0.7567349020179208</v>
-      </c>
-      <c r="E189" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>0.7270707365046987</v>
-      </c>
-      <c r="E190" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>0.7270707365046987</v>
-      </c>
-      <c r="E191" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>0.7270707365046987</v>
-      </c>
-      <c r="E192" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>0.7270707365046987</v>
-      </c>
-      <c r="E193" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>0.7254520288482553</v>
-      </c>
-      <c r="E194" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>0.7254520288482553</v>
-      </c>
-      <c r="E195" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>0.722759525023676</v>
-      </c>
-      <c r="E196" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>0.7216784439425948</v>
-      </c>
-      <c r="E197" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>0.7216784439425948</v>
-      </c>
-      <c r="E198" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>0.7216740729948278</v>
-      </c>
-      <c r="E199" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>0.7216740729948278</v>
-      </c>
-      <c r="E200" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>0.7173701464267502</v>
-      </c>
-      <c r="E201" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4667,7 +4247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4708,11 +4288,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9455336198732425</v>
+        <v>0.9711760030048655</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -4729,11 +4309,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9455336198732425</v>
+        <v>0.9711760030048655</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -4750,11 +4330,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.944994536315291</v>
+        <v>0.9707567194556301</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -4771,11 +4351,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9444510818095722</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -4792,14 +4372,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9439119982516209</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4813,14 +4393,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9439119982516209</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4834,14 +4414,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9439105412690318</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4855,14 +4435,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9439105412690318</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -4876,14 +4456,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9439105412690318</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4897,14 +4477,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9433787426240257</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -4918,14 +4498,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9433758286588475</v>
+        <v>0.970340929935972</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -4939,14 +4519,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9433758286588475</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -4960,14 +4540,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9433743716762585</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4981,14 +4561,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9433743716762585</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -5002,14 +4582,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.9433743716762585</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -5023,14 +4603,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -5044,14 +4624,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -5065,14 +4645,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -5086,14 +4666,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -5107,14 +4687,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -5128,14 +4708,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -5149,14 +4729,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -5170,14 +4750,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -5191,14 +4771,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -5212,14 +4792,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -5233,14 +4813,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9695058568670785</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -5254,14 +4834,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.9433700007284912</v>
+        <v>0.9695058568670785</v>
       </c>
       <c r="E28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -5275,14 +4855,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.9433700007284912</v>
+        <v>0.9695058568670785</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -5296,14 +4876,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9428382020834851</v>
+        <v>0.9695058568670785</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -5317,14 +4897,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.9428382020834851</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -5338,14 +4918,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.942836745100896</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -5359,14 +4939,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.9428338311357181</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
@@ -5380,14 +4960,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.9428338311357181</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
@@ -5401,14 +4981,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E35" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
@@ -5422,14 +5002,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.96950410985229</v>
       </c>
       <c r="E36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -5443,14 +5023,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.96950410985229</v>
       </c>
       <c r="E37" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -5464,14 +5044,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.9690874468252375</v>
       </c>
       <c r="E38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -5485,14 +5065,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.9686707837981849</v>
       </c>
       <c r="E39" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -5506,14 +5086,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.9686699102907907</v>
       </c>
       <c r="E40" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -5527,14 +5107,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.9686699102907907</v>
       </c>
       <c r="E41" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -5548,11 +5128,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9682532472637382</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -5569,11 +5149,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9682532472637382</v>
       </c>
       <c r="E43" t="n">
         <v>41</v>
@@ -5590,11 +5170,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9682532472637382</v>
       </c>
       <c r="E44" t="n">
         <v>41</v>
@@ -5611,11 +5191,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9682532472637382</v>
       </c>
       <c r="E45" t="n">
         <v>41</v>
@@ -5632,11 +5212,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9682532472637382</v>
       </c>
       <c r="E46" t="n">
         <v>41</v>
@@ -5653,14 +5233,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.9417585779849931</v>
+        <v>0.9682532472637382</v>
       </c>
       <c r="E47" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
@@ -5674,11 +5254,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.9417571210024039</v>
+        <v>0.968252373756344</v>
       </c>
       <c r="E48" t="n">
         <v>47</v>
@@ -5695,11 +5275,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E49" t="n">
         <v>48</v>
@@ -5716,11 +5296,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E50" t="n">
         <v>48</v>
@@ -5737,11 +5317,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E51" t="n">
         <v>48</v>
@@ -5758,11 +5338,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.9417542070372258</v>
+        <v>0.9678357107292914</v>
       </c>
       <c r="E52" t="n">
         <v>51</v>
@@ -5779,14 +5359,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.9417542070372258</v>
+        <v>0.9678348372218972</v>
       </c>
       <c r="E53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -5800,14 +5380,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.9417542070372258</v>
+        <v>0.9678339637145029</v>
       </c>
       <c r="E54" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
@@ -5821,11 +5401,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.9412194944270416</v>
+        <v>0.9674181741948447</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -5842,14 +5422,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.9412194944270416</v>
+        <v>0.967416427180056</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
@@ -5863,11 +5443,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.9412180374444524</v>
+        <v>0.9661673116062929</v>
       </c>
       <c r="E57" t="n">
         <v>56</v>
@@ -5884,11 +5464,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.9412180374444524</v>
+        <v>0.9661673116062929</v>
       </c>
       <c r="E58" t="n">
         <v>56</v>
@@ -5905,14 +5485,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.9412136664966854</v>
+        <v>0.9661673116062929</v>
       </c>
       <c r="E59" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
@@ -5926,14 +5506,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.9412136664966854</v>
+        <v>0.9657497750718461</v>
       </c>
       <c r="E60" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -5947,14 +5527,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.9406789538865011</v>
+        <v>0.9657497750718461</v>
       </c>
       <c r="E61" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62">
@@ -5968,14 +5548,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.9406789538865011</v>
+        <v>0.965746281042269</v>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63">
@@ -5989,14 +5569,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.9406789538865011</v>
+        <v>0.9653304915226109</v>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -6010,14 +5590,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.001, 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.940677496903912</v>
+        <v>0.9653304915226109</v>
       </c>
       <c r="E64" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65">
@@ -6031,11 +5611,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.940676039921323</v>
+        <v>0.9649147020029526</v>
       </c>
       <c r="E65" t="n">
         <v>64</v>
@@ -6052,11 +5632,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.940676039921323</v>
+        <v>0.9649147020029526</v>
       </c>
       <c r="E66" t="n">
         <v>64</v>
@@ -6073,11 +5653,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.9406745829387338</v>
+        <v>0.9649129549881641</v>
       </c>
       <c r="E67" t="n">
         <v>66</v>
@@ -6094,14 +5674,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.9406745829387338</v>
+        <v>0.9640796289340589</v>
       </c>
       <c r="E68" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69">
@@ -6115,11 +5695,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (20, 10), 'learning_rate_init': 0.0001, 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.9385197056895169</v>
+        <v>0.9628270193307186</v>
       </c>
       <c r="E69" t="n">
         <v>68</v>
@@ -6136,11 +5716,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (30, 20), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.9374415385736141</v>
+        <v>0.960321800124038</v>
       </c>
       <c r="E70" t="n">
         <v>69</v>
@@ -6157,11 +5737,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (100,), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.937438624608436</v>
+        <v>0.9573946768459395</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -6178,14 +5758,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.001, 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'hidden_layer_sizes': (50, 50), 'learning_rate_init': 0.0001, 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.937438624608436</v>
+        <v>0.9561403202278107</v>
       </c>
       <c r="E72" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73">
@@ -6203,7 +5783,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.9018591097836381</v>
+        <v>0.9473685589748516</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -6220,11 +5800,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.9466103300065564</v>
+        <v>0.9703400564285778</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -6241,11 +5821,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.9466103300065564</v>
+        <v>0.9703400564285778</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -6262,11 +5842,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.946072703431194</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
@@ -6283,11 +5863,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.9455321628906536</v>
+        <v>0.96950410985229</v>
       </c>
       <c r="E77" t="n">
         <v>4</v>
@@ -6304,14 +5884,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.944994536315291</v>
+        <v>0.96950410985229</v>
       </c>
       <c r="E78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -6325,11 +5905,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.9444554527573394</v>
+        <v>0.9690874468252375</v>
       </c>
       <c r="E79" t="n">
         <v>6</v>
@@ -6346,14 +5926,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.9444554527573394</v>
+        <v>0.9690865733178431</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -6367,14 +5947,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.9444554527573394</v>
+        <v>0.9690865733178431</v>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -6388,14 +5968,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.9444554527573394</v>
+        <v>0.969085699810449</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -6409,11 +5989,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.9444539957747505</v>
+        <v>0.9686699102907907</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -6430,14 +6010,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.9444539957747505</v>
+        <v>0.9682549942785267</v>
       </c>
       <c r="E84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
@@ -6451,14 +6031,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.9444539957747505</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -6472,14 +6052,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.9444539957747505</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -6493,14 +6073,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.9439163691993879</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -6514,14 +6094,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.9439163691993879</v>
+        <v>0.9678348372218972</v>
       </c>
       <c r="E88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89">
@@ -6535,11 +6115,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.943914912216799</v>
+        <v>0.9678339637145029</v>
       </c>
       <c r="E89" t="n">
         <v>16</v>
@@ -6556,11 +6136,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9674181741948447</v>
       </c>
       <c r="E90" t="n">
         <v>17</v>
@@ -6577,11 +6157,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.9428367451008961</v>
+        <v>0.9674173006874505</v>
       </c>
       <c r="E91" t="n">
         <v>18</v>
@@ -6598,11 +6178,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.9422991185255336</v>
+        <v>0.967416427180056</v>
       </c>
       <c r="E92" t="n">
         <v>19</v>
@@ -6619,11 +6199,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.9422991185255336</v>
+        <v>0.967416427180056</v>
       </c>
       <c r="E93" t="n">
         <v>19</v>
@@ -6640,11 +6220,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.9422962045603555</v>
+        <v>0.9669997641530037</v>
       </c>
       <c r="E94" t="n">
         <v>21</v>
@@ -6661,11 +6241,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9665857216481338</v>
       </c>
       <c r="E95" t="n">
         <v>22</v>
@@ -6682,14 +6262,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9661638175767159</v>
       </c>
       <c r="E96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
@@ -6703,11 +6283,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.9417542070372258</v>
+        <v>0.9657489015644518</v>
       </c>
       <c r="E97" t="n">
         <v>24</v>
@@ -6724,11 +6304,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.9412165804618635</v>
+        <v>0.9644962919611114</v>
       </c>
       <c r="E98" t="n">
         <v>25</v>
@@ -6745,14 +6325,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.9412165804618635</v>
+        <v>0.9640778819192706</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100">
@@ -6766,11 +6346,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.9401369563633715</v>
+        <v>0.9640770084118764</v>
       </c>
       <c r="E100" t="n">
         <v>27</v>
@@ -6787,14 +6367,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.9401369563633715</v>
+        <v>0.9632419353429826</v>
       </c>
       <c r="E101" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102">
@@ -6803,19 +6383,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.9401354993807824</v>
+        <v>0.9707584664704187</v>
       </c>
       <c r="E102" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6824,19 +6404,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.93959787280542</v>
+        <v>0.9707584664704187</v>
       </c>
       <c r="E103" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6845,19 +6425,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.9395964158228309</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E104" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -6866,19 +6446,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.9395964158228309</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E105" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -6887,19 +6467,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.9395964158228309</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E106" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -6908,19 +6488,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.9395964158228309</v>
+        <v>0.9699233934015252</v>
       </c>
       <c r="E107" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -6929,19 +6509,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.9395964158228309</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E108" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -6950,19 +6530,19 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.9390515043345232</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E109" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -6971,19 +6551,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.9390515043345232</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E110" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -6992,19 +6572,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.9385138777591606</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E111" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -7013,19 +6593,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.9385138777591606</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E112" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -7034,19 +6614,19 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.9379791651489764</v>
+        <v>0.969922519894131</v>
       </c>
       <c r="E113" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -7055,19 +6635,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.9379791651489764</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E114" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
@@ -7076,19 +6656,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.9379762511837983</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E115" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
@@ -7097,19 +6677,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.9368980840678953</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E116" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
@@ -7118,19 +6698,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.9368980840678953</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E117" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
@@ -7139,19 +6719,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.9363546295621766</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E118" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
@@ -7160,19 +6740,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.9363546295621766</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E119" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
@@ -7181,19 +6761,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.9358170029868143</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E120" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
@@ -7202,19 +6782,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.9358170029868143</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E121" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122">
@@ -7228,14 +6808,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.9444496248269834</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123">
@@ -7249,14 +6829,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.9444496248269834</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124">
@@ -7270,14 +6850,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.9444496248269832</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125">
@@ -7291,14 +6871,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.9444496248269832</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E125" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126">
@@ -7312,14 +6892,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.9439119982516209</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E126" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
@@ -7333,14 +6913,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.9439119982516206</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E127" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128">
@@ -7354,14 +6934,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.9433729146936694</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E128" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129">
@@ -7375,14 +6955,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.9433714577110803</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E129" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130">
@@ -7396,14 +6976,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.9433714577110802</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E130" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131">
@@ -7417,14 +6997,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.9433700007284912</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E131" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132">
@@ -7438,14 +7018,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.9433700007284912</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E132" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133">
@@ -7459,14 +7039,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.9428323741531288</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134">
@@ -7480,11 +7060,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.9428309171705399</v>
+        <v>0.9695049833596843</v>
       </c>
       <c r="E134" t="n">
         <v>13</v>
@@ -7501,14 +7081,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.9428309171705397</v>
+        <v>0.96950410985229</v>
       </c>
       <c r="E135" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
@@ -7522,14 +7102,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.9428309171705397</v>
+        <v>0.96950410985229</v>
       </c>
       <c r="E136" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137">
@@ -7543,14 +7123,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9690883203326317</v>
       </c>
       <c r="E137" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138">
@@ -7564,14 +7144,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9690883203326317</v>
       </c>
       <c r="E138" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="139">
@@ -7585,14 +7165,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9686707837981849</v>
       </c>
       <c r="E139" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140">
@@ -7606,14 +7186,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9686707837981849</v>
       </c>
       <c r="E140" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141">
@@ -7627,14 +7207,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9682515002489496</v>
       </c>
       <c r="E141" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142">
@@ -7648,14 +7228,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9678357107292914</v>
       </c>
       <c r="E142" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143">
@@ -7669,14 +7249,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9678357107292914</v>
       </c>
       <c r="E143" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="144">
@@ -7690,14 +7270,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.9422947475777665</v>
+        <v>0.9661638175767159</v>
       </c>
       <c r="E144" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145">
@@ -7711,14 +7291,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9657497750718459</v>
       </c>
       <c r="E145" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146">
@@ -7732,14 +7312,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9653304915226106</v>
       </c>
       <c r="E146" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147">
@@ -7753,14 +7333,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9653304915226106</v>
       </c>
       <c r="E147" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="148">
@@ -7774,14 +7354,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.9422932905951773</v>
+        <v>0.9644971654685056</v>
       </c>
       <c r="E148" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149">
@@ -7795,14 +7375,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9644971654685056</v>
       </c>
       <c r="E149" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150">
@@ -7816,14 +7396,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9644936714389288</v>
       </c>
       <c r="E150" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="151">
@@ -7837,14 +7417,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9640796289340589</v>
       </c>
       <c r="E151" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="152">
@@ -7858,14 +7438,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9640796289340589</v>
       </c>
       <c r="E152" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="153">
@@ -7879,14 +7459,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9640796289340589</v>
       </c>
       <c r="E153" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="154">
@@ -7900,14 +7480,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.941755664019815</v>
+        <v>0.964076134904482</v>
       </c>
       <c r="E154" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="155">
@@ -7921,14 +7501,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.941755664019815</v>
+        <v>0.964076134904482</v>
       </c>
       <c r="E155" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="156">
@@ -7942,14 +7522,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9594832330255676</v>
       </c>
       <c r="E156" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157">
@@ -7963,14 +7543,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9390204488080991</v>
       </c>
       <c r="E157" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="158">
@@ -7984,14 +7564,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.941755664019815</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E158" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="159">
@@ -8005,14 +7585,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.941755664019815</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E159" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="160">
@@ -8026,14 +7606,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.941755664019815</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E160" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="161">
@@ -8047,14 +7627,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.941755664019815</v>
+        <v>0.5000078615665482</v>
       </c>
       <c r="E161" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="162">
@@ -8063,19 +7643,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9678339637145029</v>
       </c>
       <c r="E162" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -8084,19 +7664,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.941755664019815</v>
+        <v>0.967415553672662</v>
       </c>
       <c r="E163" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -8105,19 +7685,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9669988906456094</v>
       </c>
       <c r="E164" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
@@ -8126,19 +7706,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9661638175767159</v>
       </c>
       <c r="E165" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
@@ -8147,19 +7727,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.941755664019815</v>
+        <v>0.9657480280570576</v>
       </c>
       <c r="E166" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -8168,19 +7748,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.9412165804618635</v>
+        <v>0.9649129549881641</v>
       </c>
       <c r="E167" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
@@ -8189,19 +7769,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.9412165804618635</v>
+        <v>0.9649112079733755</v>
       </c>
       <c r="E168" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -8210,19 +7790,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.9412165804618635</v>
+        <v>0.9649112079733755</v>
       </c>
       <c r="E169" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -8231,19 +7811,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.9412151234792743</v>
+        <v>0.9649112079733755</v>
       </c>
       <c r="E170" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -8252,19 +7832,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.940674582938734</v>
+        <v>0.9649112079733755</v>
       </c>
       <c r="E171" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -8273,19 +7853,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.9406745829387338</v>
+        <v>0.9649112079733755</v>
       </c>
       <c r="E172" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
@@ -8294,19 +7874,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.9406731259561448</v>
+        <v>0.9649112079733755</v>
       </c>
       <c r="E173" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174">
@@ -8315,19 +7895,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.9401384133459605</v>
+        <v>0.9644945449463231</v>
       </c>
       <c r="E174" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
@@ -8336,19 +7916,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.939599329788009</v>
+        <v>0.9644945449463231</v>
       </c>
       <c r="E175" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -8357,19 +7937,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.937438624608436</v>
+        <v>0.9644936714389288</v>
       </c>
       <c r="E176" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177">
@@ -8378,19 +7958,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.9352852043418081</v>
+        <v>0.9644936714389288</v>
       </c>
       <c r="E177" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
@@ -8399,19 +7979,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.499998543017411</v>
+        <v>0.9644936714389288</v>
       </c>
       <c r="E178" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179">
@@ -8420,19 +8000,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.499998543017411</v>
+        <v>0.9628217782863533</v>
       </c>
       <c r="E179" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180">
@@ -8441,19 +8021,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.499998543017411</v>
+        <v>0.9619884522322483</v>
       </c>
       <c r="E180" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181">
@@ -8462,438 +8042,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.499998543017411</v>
+        <v>0.9619858317100654</v>
       </c>
       <c r="E181" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>0.94391345523421</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>0.94391345523421</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>0.9433714577110803</v>
-      </c>
-      <c r="E184" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>0.9428338311357181</v>
-      </c>
-      <c r="E185" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>0.9428338311357181</v>
-      </c>
-      <c r="E186" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>0.9428338311357181</v>
-      </c>
-      <c r="E187" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>0.9428338311357181</v>
-      </c>
-      <c r="E188" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>0.9428323741531288</v>
-      </c>
-      <c r="E189" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>0.9422947475777665</v>
-      </c>
-      <c r="E190" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>0.9422947475777665</v>
-      </c>
-      <c r="E191" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>0.9422947475777665</v>
-      </c>
-      <c r="E192" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'linear'}</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>0.9422947475777665</v>
-      </c>
-      <c r="E193" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>0.9422932905951773</v>
-      </c>
-      <c r="E194" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>0.9412136664966854</v>
-      </c>
-      <c r="E195" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>0.9406760399213228</v>
-      </c>
-      <c r="E196" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>0.9395964158228308</v>
-      </c>
-      <c r="E197" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>0.9390602462300575</v>
-      </c>
-      <c r="E198" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>0.9390573322648794</v>
-      </c>
-      <c r="E199" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>0.9374459095213814</v>
-      </c>
-      <c r="E200" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>0.9352852043418082</v>
-      </c>
-      <c r="E201" t="n">
         <v>20</v>
       </c>
     </row>
